--- a/review-results/河北实时运行及市场出清数据-20260903.xlsx
+++ b/review-results/河北实时运行及市场出清数据-20260903.xlsx
@@ -4092,8 +4092,12 @@
       <s:c r="C2" s="1" t="n">
         <s:v>1</s:v>
       </s:c>
-      <s:c r="D2" s="1"/>
-      <s:c r="E2" s="1"/>
+      <s:c r="D2" s="1" t="n">
+        <s:v>385.6</s:v>
+      </s:c>
+      <s:c r="E2" s="1" t="n">
+        <s:v>392.11</s:v>
+      </s:c>
       <s:c r="F2" s="1" t="n">
         <s:v>425</s:v>
       </s:c>
@@ -4138,8 +4142,12 @@
       <s:c r="C3" s="1" t="n">
         <s:v>1</s:v>
       </s:c>
-      <s:c r="D3" s="1"/>
-      <s:c r="E3" s="1"/>
+      <s:c r="D3" s="1" t="n">
+        <s:v>385.6</s:v>
+      </s:c>
+      <s:c r="E3" s="1" t="n">
+        <s:v>395.89</s:v>
+      </s:c>
       <s:c r="F3" s="1" t="n">
         <s:v>655</s:v>
       </s:c>
@@ -4184,8 +4192,12 @@
       <s:c r="C4" s="1" t="n">
         <s:v>1</s:v>
       </s:c>
-      <s:c r="D4" s="1"/>
-      <s:c r="E4" s="1"/>
+      <s:c r="D4" s="1" t="n">
+        <s:v>385.6</s:v>
+      </s:c>
+      <s:c r="E4" s="1" t="n">
+        <s:v>403.39</s:v>
+      </s:c>
       <s:c r="F4" s="1" t="n">
         <s:v>655</s:v>
       </s:c>
@@ -4230,8 +4242,12 @@
       <s:c r="C5" s="1" t="n">
         <s:v>1</s:v>
       </s:c>
-      <s:c r="D5" s="1"/>
-      <s:c r="E5" s="1"/>
+      <s:c r="D5" s="1" t="n">
+        <s:v>385.6</s:v>
+      </s:c>
+      <s:c r="E5" s="1" t="n">
+        <s:v>414.36</s:v>
+      </s:c>
       <s:c r="F5" s="1" t="n">
         <s:v>425</s:v>
       </s:c>
@@ -4276,8 +4292,12 @@
       <s:c r="C6" s="1" t="n">
         <s:v>2</s:v>
       </s:c>
-      <s:c r="D6" s="1"/>
-      <s:c r="E6" s="1"/>
+      <s:c r="D6" s="1" t="n">
+        <s:v>385.6</s:v>
+      </s:c>
+      <s:c r="E6" s="1" t="n">
+        <s:v>423.64</s:v>
+      </s:c>
       <s:c r="F6" s="1" t="n">
         <s:v>175</s:v>
       </s:c>
@@ -4322,8 +4342,12 @@
       <s:c r="C7" s="1" t="n">
         <s:v>2</s:v>
       </s:c>
-      <s:c r="D7" s="1"/>
-      <s:c r="E7" s="1"/>
+      <s:c r="D7" s="1" t="n">
+        <s:v>385.6</s:v>
+      </s:c>
+      <s:c r="E7" s="1" t="n">
+        <s:v>405.29</s:v>
+      </s:c>
       <s:c r="F7" s="1" t="n">
         <s:v>205</s:v>
       </s:c>
@@ -4368,8 +4392,12 @@
       <s:c r="C8" s="1" t="n">
         <s:v>2</s:v>
       </s:c>
-      <s:c r="D8" s="1"/>
-      <s:c r="E8" s="1"/>
+      <s:c r="D8" s="1" t="n">
+        <s:v>385.6</s:v>
+      </s:c>
+      <s:c r="E8" s="1" t="n">
+        <s:v>402.11</s:v>
+      </s:c>
       <s:c r="F8" s="1" t="n">
         <s:v>205</s:v>
       </s:c>
@@ -4414,8 +4442,12 @@
       <s:c r="C9" s="1" t="n">
         <s:v>2</s:v>
       </s:c>
-      <s:c r="D9" s="1"/>
-      <s:c r="E9" s="1"/>
+      <s:c r="D9" s="1" t="n">
+        <s:v>385.6</s:v>
+      </s:c>
+      <s:c r="E9" s="1" t="n">
+        <s:v>395.97</s:v>
+      </s:c>
       <s:c r="F9" s="1" t="n">
         <s:v>150</s:v>
       </s:c>
@@ -4460,8 +4492,12 @@
       <s:c r="C10" s="1" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="D10" s="1"/>
-      <s:c r="E10" s="1"/>
+      <s:c r="D10" s="1" t="n">
+        <s:v>393.01</s:v>
+      </s:c>
+      <s:c r="E10" s="1" t="n">
+        <s:v>414.17</s:v>
+      </s:c>
       <s:c r="F10" s="1" t="n">
         <s:v>430</s:v>
       </s:c>
@@ -4506,8 +4542,12 @@
       <s:c r="C11" s="1" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="D11" s="1"/>
-      <s:c r="E11" s="1"/>
+      <s:c r="D11" s="1" t="n">
+        <s:v>393.01</s:v>
+      </s:c>
+      <s:c r="E11" s="1" t="n">
+        <s:v>419.38</s:v>
+      </s:c>
       <s:c r="F11" s="1" t="n">
         <s:v>580</s:v>
       </s:c>
@@ -4552,8 +4592,12 @@
       <s:c r="C12" s="1" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="D12" s="1"/>
-      <s:c r="E12" s="1"/>
+      <s:c r="D12" s="1" t="n">
+        <s:v>393.01</s:v>
+      </s:c>
+      <s:c r="E12" s="1" t="n">
+        <s:v>415.42</s:v>
+      </s:c>
       <s:c r="F12" s="1" t="n">
         <s:v>670</s:v>
       </s:c>
@@ -4598,8 +4642,12 @@
       <s:c r="C13" s="1" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="D13" s="1"/>
-      <s:c r="E13" s="1"/>
+      <s:c r="D13" s="1" t="n">
+        <s:v>393.01</s:v>
+      </s:c>
+      <s:c r="E13" s="1" t="n">
+        <s:v>414.36</s:v>
+      </s:c>
       <s:c r="F13" s="1" t="n">
         <s:v>720</s:v>
       </s:c>
@@ -4644,8 +4692,12 @@
       <s:c r="C14" s="1" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D14" s="1"/>
-      <s:c r="E14" s="1"/>
+      <s:c r="D14" s="1" t="n">
+        <s:v>393.01</s:v>
+      </s:c>
+      <s:c r="E14" s="1" t="n">
+        <s:v>404.23</s:v>
+      </s:c>
       <s:c r="F14" s="1" t="n">
         <s:v>750</s:v>
       </s:c>
@@ -4690,8 +4742,12 @@
       <s:c r="C15" s="1" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D15" s="1"/>
-      <s:c r="E15" s="1"/>
+      <s:c r="D15" s="1" t="n">
+        <s:v>393.01</s:v>
+      </s:c>
+      <s:c r="E15" s="1" t="n">
+        <s:v>395.41</s:v>
+      </s:c>
       <s:c r="F15" s="1" t="n">
         <s:v>993</s:v>
       </s:c>
@@ -4736,8 +4792,12 @@
       <s:c r="C16" s="1" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D16" s="1"/>
-      <s:c r="E16" s="1"/>
+      <s:c r="D16" s="1" t="n">
+        <s:v>393.01</s:v>
+      </s:c>
+      <s:c r="E16" s="1" t="n">
+        <s:v>402.41</s:v>
+      </s:c>
       <s:c r="F16" s="1" t="n">
         <s:v>1061</s:v>
       </s:c>
@@ -4782,8 +4842,12 @@
       <s:c r="C17" s="1" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D17" s="1"/>
-      <s:c r="E17" s="1"/>
+      <s:c r="D17" s="1" t="n">
+        <s:v>393.01</s:v>
+      </s:c>
+      <s:c r="E17" s="1" t="n">
+        <s:v>403.39</s:v>
+      </s:c>
       <s:c r="F17" s="1" t="n">
         <s:v>1091</s:v>
       </s:c>
@@ -4828,8 +4892,12 @@
       <s:c r="C18" s="1" t="n">
         <s:v>5</s:v>
       </s:c>
-      <s:c r="D18" s="1"/>
-      <s:c r="E18" s="1"/>
+      <s:c r="D18" s="1" t="n">
+        <s:v>385.6</s:v>
+      </s:c>
+      <s:c r="E18" s="1" t="n">
+        <s:v>394.67</s:v>
+      </s:c>
       <s:c r="F18" s="1" t="n">
         <s:v>1391</s:v>
       </s:c>
@@ -4874,8 +4942,12 @@
       <s:c r="C19" s="1" t="n">
         <s:v>5</s:v>
       </s:c>
-      <s:c r="D19" s="1"/>
-      <s:c r="E19" s="1"/>
+      <s:c r="D19" s="1" t="n">
+        <s:v>385.6</s:v>
+      </s:c>
+      <s:c r="E19" s="1" t="n">
+        <s:v>394.45</s:v>
+      </s:c>
       <s:c r="F19" s="1" t="n">
         <s:v>1481</s:v>
       </s:c>
@@ -4920,8 +4992,12 @@
       <s:c r="C20" s="1" t="n">
         <s:v>5</s:v>
       </s:c>
-      <s:c r="D20" s="1"/>
-      <s:c r="E20" s="1"/>
+      <s:c r="D20" s="1" t="n">
+        <s:v>385.6</s:v>
+      </s:c>
+      <s:c r="E20" s="1" t="n">
+        <s:v>393.98</s:v>
+      </s:c>
       <s:c r="F20" s="1" t="n">
         <s:v>1481</s:v>
       </s:c>
@@ -4966,8 +5042,12 @@
       <s:c r="C21" s="1" t="n">
         <s:v>5</s:v>
       </s:c>
-      <s:c r="D21" s="1"/>
-      <s:c r="E21" s="1"/>
+      <s:c r="D21" s="1" t="n">
+        <s:v>385.6</s:v>
+      </s:c>
+      <s:c r="E21" s="1" t="n">
+        <s:v>394.67</s:v>
+      </s:c>
       <s:c r="F21" s="1" t="n">
         <s:v>1391</s:v>
       </s:c>
@@ -5012,8 +5092,12 @@
       <s:c r="C22" s="1" t="n">
         <s:v>6</s:v>
       </s:c>
-      <s:c r="D22" s="1"/>
-      <s:c r="E22" s="1"/>
+      <s:c r="D22" s="1" t="n">
+        <s:v>393.01</s:v>
+      </s:c>
+      <s:c r="E22" s="1" t="n">
+        <s:v>387.92</s:v>
+      </s:c>
       <s:c r="F22" s="1" t="n">
         <s:v>2221</s:v>
       </s:c>
@@ -5058,8 +5142,12 @@
       <s:c r="C23" s="1" t="n">
         <s:v>6</s:v>
       </s:c>
-      <s:c r="D23" s="1"/>
-      <s:c r="E23" s="1"/>
+      <s:c r="D23" s="1" t="n">
+        <s:v>393.01</s:v>
+      </s:c>
+      <s:c r="E23" s="1" t="n">
+        <s:v>386.79</s:v>
+      </s:c>
       <s:c r="F23" s="1" t="n">
         <s:v>2526</s:v>
       </s:c>
@@ -5104,8 +5192,12 @@
       <s:c r="C24" s="1" t="n">
         <s:v>6</s:v>
       </s:c>
-      <s:c r="D24" s="1"/>
-      <s:c r="E24" s="1"/>
+      <s:c r="D24" s="1" t="n">
+        <s:v>393.01</s:v>
+      </s:c>
+      <s:c r="E24" s="1" t="n">
+        <s:v>404.23</s:v>
+      </s:c>
       <s:c r="F24" s="1" t="n">
         <s:v>2461</s:v>
       </s:c>
@@ -5150,8 +5242,12 @@
       <s:c r="C25" s="1" t="n">
         <s:v>6</s:v>
       </s:c>
-      <s:c r="D25" s="1"/>
-      <s:c r="E25" s="1"/>
+      <s:c r="D25" s="1" t="n">
+        <s:v>393.01</s:v>
+      </s:c>
+      <s:c r="E25" s="1" t="n">
+        <s:v>404.72</s:v>
+      </s:c>
       <s:c r="F25" s="1" t="n">
         <s:v>2431</s:v>
       </s:c>
@@ -5196,8 +5292,12 @@
       <s:c r="C26" s="1" t="n">
         <s:v>7</s:v>
       </s:c>
-      <s:c r="D26" s="1"/>
-      <s:c r="E26" s="1"/>
+      <s:c r="D26" s="1" t="n">
+        <s:v>393.98</s:v>
+      </s:c>
+      <s:c r="E26" s="1" t="n">
+        <s:v>416.45</s:v>
+      </s:c>
       <s:c r="F26" s="1" t="n">
         <s:v>2293</s:v>
       </s:c>
@@ -5242,8 +5342,12 @@
       <s:c r="C27" s="1" t="n">
         <s:v>7</s:v>
       </s:c>
-      <s:c r="D27" s="1"/>
-      <s:c r="E27" s="1"/>
+      <s:c r="D27" s="1" t="n">
+        <s:v>393.98</s:v>
+      </s:c>
+      <s:c r="E27" s="1" t="n">
+        <s:v>405.36</s:v>
+      </s:c>
       <s:c r="F27" s="1" t="n">
         <s:v>2128</s:v>
       </s:c>
@@ -5288,8 +5392,12 @@
       <s:c r="C28" s="1" t="n">
         <s:v>7</s:v>
       </s:c>
-      <s:c r="D28" s="1"/>
-      <s:c r="E28" s="1"/>
+      <s:c r="D28" s="1" t="n">
+        <s:v>393.98</s:v>
+      </s:c>
+      <s:c r="E28" s="1" t="n">
+        <s:v>404.98</s:v>
+      </s:c>
       <s:c r="F28" s="1" t="n">
         <s:v>1978</s:v>
       </s:c>
@@ -5334,8 +5442,12 @@
       <s:c r="C29" s="1" t="n">
         <s:v>7</s:v>
       </s:c>
-      <s:c r="D29" s="1"/>
-      <s:c r="E29" s="1"/>
+      <s:c r="D29" s="1" t="n">
+        <s:v>393.98</s:v>
+      </s:c>
+      <s:c r="E29" s="1" t="n">
+        <s:v>404.23</s:v>
+      </s:c>
       <s:c r="F29" s="1" t="n">
         <s:v>1538</s:v>
       </s:c>
@@ -5380,8 +5492,12 @@
       <s:c r="C30" s="1" t="n">
         <s:v>8</s:v>
       </s:c>
-      <s:c r="D30" s="1"/>
-      <s:c r="E30" s="1"/>
+      <s:c r="D30" s="1" t="n">
+        <s:v>385.6</s:v>
+      </s:c>
+      <s:c r="E30" s="1" t="n">
+        <s:v>417.25</s:v>
+      </s:c>
       <s:c r="F30" s="1" t="n">
         <s:v>810</s:v>
       </s:c>
@@ -5426,8 +5542,12 @@
       <s:c r="C31" s="1" t="n">
         <s:v>8</s:v>
       </s:c>
-      <s:c r="D31" s="1"/>
-      <s:c r="E31" s="1"/>
+      <s:c r="D31" s="1" t="n">
+        <s:v>385.6</s:v>
+      </s:c>
+      <s:c r="E31" s="1" t="n">
+        <s:v>417.95</s:v>
+      </s:c>
       <s:c r="F31" s="1" t="n">
         <s:v>320</s:v>
       </s:c>
@@ -5472,8 +5592,12 @@
       <s:c r="C32" s="1" t="n">
         <s:v>8</s:v>
       </s:c>
-      <s:c r="D32" s="1"/>
-      <s:c r="E32" s="1"/>
+      <s:c r="D32" s="1" t="n">
+        <s:v>385.6</s:v>
+      </s:c>
+      <s:c r="E32" s="1" t="n">
+        <s:v>404.72</s:v>
+      </s:c>
       <s:c r="F32" s="1" t="n">
         <s:v>120</s:v>
       </s:c>
@@ -5518,8 +5642,12 @@
       <s:c r="C33" s="1" t="n">
         <s:v>8</s:v>
       </s:c>
-      <s:c r="D33" s="1"/>
-      <s:c r="E33" s="1"/>
+      <s:c r="D33" s="1" t="n">
+        <s:v>385.6</s:v>
+      </s:c>
+      <s:c r="E33" s="1" t="n">
+        <s:v>392.8</s:v>
+      </s:c>
       <s:c r="F33" s="1" t="n">
         <s:v>90</s:v>
       </s:c>
@@ -5564,8 +5692,12 @@
       <s:c r="C34" s="1" t="n">
         <s:v>9</s:v>
       </s:c>
-      <s:c r="D34" s="1"/>
-      <s:c r="E34" s="1"/>
+      <s:c r="D34" s="1" t="n">
+        <s:v>350</s:v>
+      </s:c>
+      <s:c r="E34" s="1" t="n">
+        <s:v>383.92</s:v>
+      </s:c>
       <s:c r="F34" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -5610,8 +5742,12 @@
       <s:c r="C35" s="1" t="n">
         <s:v>9</s:v>
       </s:c>
-      <s:c r="D35" s="1"/>
-      <s:c r="E35" s="1"/>
+      <s:c r="D35" s="1" t="n">
+        <s:v>350</s:v>
+      </s:c>
+      <s:c r="E35" s="1" t="n">
+        <s:v>367.11</s:v>
+      </s:c>
       <s:c r="F35" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -5656,8 +5792,12 @@
       <s:c r="C36" s="1" t="n">
         <s:v>9</s:v>
       </s:c>
-      <s:c r="D36" s="1"/>
-      <s:c r="E36" s="1"/>
+      <s:c r="D36" s="1" t="n">
+        <s:v>350</s:v>
+      </s:c>
+      <s:c r="E36" s="1" t="n">
+        <s:v>350.76</s:v>
+      </s:c>
       <s:c r="F36" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -5702,8 +5842,12 @@
       <s:c r="C37" s="1" t="n">
         <s:v>9</s:v>
       </s:c>
-      <s:c r="D37" s="1"/>
-      <s:c r="E37" s="1"/>
+      <s:c r="D37" s="1" t="n">
+        <s:v>366.14</s:v>
+      </s:c>
+      <s:c r="E37" s="1" t="n">
+        <s:v>349.42</s:v>
+      </s:c>
       <s:c r="F37" s="1" t="n">
         <s:v>-100</s:v>
       </s:c>
@@ -5748,8 +5892,12 @@
       <s:c r="C38" s="1" t="n">
         <s:v>10</s:v>
       </s:c>
-      <s:c r="D38" s="1"/>
-      <s:c r="E38" s="1"/>
+      <s:c r="D38" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="E38" s="1" t="n">
+        <s:v>357.47</s:v>
+      </s:c>
       <s:c r="F38" s="1" t="n">
         <s:v>-1242</s:v>
       </s:c>
@@ -5794,8 +5942,12 @@
       <s:c r="C39" s="1" t="n">
         <s:v>10</s:v>
       </s:c>
-      <s:c r="D39" s="1"/>
-      <s:c r="E39" s="1"/>
+      <s:c r="D39" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="E39" s="1" t="n">
+        <s:v>350</s:v>
+      </s:c>
       <s:c r="F39" s="1" t="n">
         <s:v>-1665</s:v>
       </s:c>
@@ -5840,8 +5992,12 @@
       <s:c r="C40" s="1" t="n">
         <s:v>10</s:v>
       </s:c>
-      <s:c r="D40" s="1"/>
-      <s:c r="E40" s="1"/>
+      <s:c r="D40" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="E40" s="1" t="n">
+        <s:v>348.01</s:v>
+      </s:c>
       <s:c r="F40" s="1" t="n">
         <s:v>-2341</s:v>
       </s:c>
@@ -5886,8 +6042,12 @@
       <s:c r="C41" s="1" t="n">
         <s:v>10</s:v>
       </s:c>
-      <s:c r="D41" s="1"/>
-      <s:c r="E41" s="1"/>
+      <s:c r="D41" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="E41" s="1" t="n">
+        <s:v>348.57</s:v>
+      </s:c>
       <s:c r="F41" s="1" t="n">
         <s:v>-2816</s:v>
       </s:c>
@@ -5932,8 +6092,12 @@
       <s:c r="C42" s="1" t="n">
         <s:v>11</s:v>
       </s:c>
-      <s:c r="D42" s="1"/>
-      <s:c r="E42" s="1"/>
+      <s:c r="D42" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="E42" s="1" t="n">
+        <s:v>347.95</s:v>
+      </s:c>
       <s:c r="F42" s="1" t="n">
         <s:v>-3415</s:v>
       </s:c>
@@ -5978,8 +6142,12 @@
       <s:c r="C43" s="1" t="n">
         <s:v>11</s:v>
       </s:c>
-      <s:c r="D43" s="1"/>
-      <s:c r="E43" s="1"/>
+      <s:c r="D43" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="E43" s="1" t="n">
+        <s:v>349.42</s:v>
+      </s:c>
       <s:c r="F43" s="1" t="n">
         <s:v>-3625</s:v>
       </s:c>
@@ -6024,8 +6192,12 @@
       <s:c r="C44" s="1" t="n">
         <s:v>11</s:v>
       </s:c>
-      <s:c r="D44" s="1"/>
-      <s:c r="E44" s="1"/>
+      <s:c r="D44" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="E44" s="1" t="n">
+        <s:v>347.17</s:v>
+      </s:c>
       <s:c r="F44" s="1" t="n">
         <s:v>-3785</s:v>
       </s:c>
@@ -6070,8 +6242,12 @@
       <s:c r="C45" s="1" t="n">
         <s:v>11</s:v>
       </s:c>
-      <s:c r="D45" s="1"/>
-      <s:c r="E45" s="1"/>
+      <s:c r="D45" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="E45" s="1" t="n">
+        <s:v>347.47</s:v>
+      </s:c>
       <s:c r="F45" s="1" t="n">
         <s:v>-3755</s:v>
       </s:c>
@@ -6116,8 +6292,12 @@
       <s:c r="C46" s="1" t="n">
         <s:v>12</s:v>
       </s:c>
-      <s:c r="D46" s="1"/>
-      <s:c r="E46" s="1"/>
+      <s:c r="D46" s="1" t="n">
+        <s:v>1200</s:v>
+      </s:c>
+      <s:c r="E46" s="1" t="n">
+        <s:v>347.47</s:v>
+      </s:c>
       <s:c r="F46" s="1" t="n">
         <s:v>-3315</s:v>
       </s:c>
@@ -6162,8 +6342,12 @@
       <s:c r="C47" s="1" t="n">
         <s:v>12</s:v>
       </s:c>
-      <s:c r="D47" s="1"/>
-      <s:c r="E47" s="1"/>
+      <s:c r="D47" s="1" t="n">
+        <s:v>1200</s:v>
+      </s:c>
+      <s:c r="E47" s="1" t="n">
+        <s:v>360.14</s:v>
+      </s:c>
       <s:c r="F47" s="1" t="n">
         <s:v>-3170</s:v>
       </s:c>
@@ -6208,8 +6392,12 @@
       <s:c r="C48" s="1" t="n">
         <s:v>12</s:v>
       </s:c>
-      <s:c r="D48" s="1"/>
-      <s:c r="E48" s="1"/>
+      <s:c r="D48" s="1" t="n">
+        <s:v>1200</s:v>
+      </s:c>
+      <s:c r="E48" s="1" t="n">
+        <s:v>348.25</s:v>
+      </s:c>
       <s:c r="F48" s="1" t="n">
         <s:v>-3070</s:v>
       </s:c>
@@ -6254,8 +6442,12 @@
       <s:c r="C49" s="1" t="n">
         <s:v>12</s:v>
       </s:c>
-      <s:c r="D49" s="1"/>
-      <s:c r="E49" s="1"/>
+      <s:c r="D49" s="1" t="n">
+        <s:v>1200</s:v>
+      </s:c>
+      <s:c r="E49" s="1" t="n">
+        <s:v>353.76</s:v>
+      </s:c>
       <s:c r="F49" s="1" t="n">
         <s:v>-3120</s:v>
       </s:c>
@@ -6300,8 +6492,12 @@
       <s:c r="C50" s="1" t="n">
         <s:v>13</s:v>
       </s:c>
-      <s:c r="D50" s="1"/>
-      <s:c r="E50" s="1"/>
+      <s:c r="D50" s="1" t="n">
+        <s:v>1200</s:v>
+      </s:c>
+      <s:c r="E50" s="1" t="n">
+        <s:v>346.95</s:v>
+      </s:c>
       <s:c r="F50" s="1" t="n">
         <s:v>-3080</s:v>
       </s:c>
@@ -6346,8 +6542,12 @@
       <s:c r="C51" s="1" t="n">
         <s:v>13</s:v>
       </s:c>
-      <s:c r="D51" s="1"/>
-      <s:c r="E51" s="1"/>
+      <s:c r="D51" s="1" t="n">
+        <s:v>1200</s:v>
+      </s:c>
+      <s:c r="E51" s="1" t="n">
+        <s:v>348.25</s:v>
+      </s:c>
       <s:c r="F51" s="1" t="n">
         <s:v>-3090</s:v>
       </s:c>
@@ -6392,8 +6592,12 @@
       <s:c r="C52" s="1" t="n">
         <s:v>13</s:v>
       </s:c>
-      <s:c r="D52" s="1"/>
-      <s:c r="E52" s="1"/>
+      <s:c r="D52" s="1" t="n">
+        <s:v>1200</s:v>
+      </s:c>
+      <s:c r="E52" s="1" t="n">
+        <s:v>348.51</s:v>
+      </s:c>
       <s:c r="F52" s="1" t="n">
         <s:v>-3024</s:v>
       </s:c>
@@ -6438,8 +6642,12 @@
       <s:c r="C53" s="1" t="n">
         <s:v>13</s:v>
       </s:c>
-      <s:c r="D53" s="1"/>
-      <s:c r="E53" s="1"/>
+      <s:c r="D53" s="1" t="n">
+        <s:v>1200</s:v>
+      </s:c>
+      <s:c r="E53" s="1" t="n">
+        <s:v>349.42</s:v>
+      </s:c>
       <s:c r="F53" s="1" t="n">
         <s:v>-2931</s:v>
       </s:c>
@@ -6484,8 +6692,12 @@
       <s:c r="C54" s="1" t="n">
         <s:v>14</s:v>
       </s:c>
-      <s:c r="D54" s="1"/>
-      <s:c r="E54" s="1"/>
+      <s:c r="D54" s="1" t="n">
+        <s:v>1200</s:v>
+      </s:c>
+      <s:c r="E54" s="1" t="n">
+        <s:v>350.76</s:v>
+      </s:c>
       <s:c r="F54" s="1" t="n">
         <s:v>-2947</s:v>
       </s:c>
@@ -6530,8 +6742,12 @@
       <s:c r="C55" s="1" t="n">
         <s:v>14</s:v>
       </s:c>
-      <s:c r="D55" s="1"/>
-      <s:c r="E55" s="1"/>
+      <s:c r="D55" s="1" t="n">
+        <s:v>1200</s:v>
+      </s:c>
+      <s:c r="E55" s="1" t="n">
+        <s:v>350.76</s:v>
+      </s:c>
       <s:c r="F55" s="1" t="n">
         <s:v>-2767</s:v>
       </s:c>
@@ -6576,8 +6792,12 @@
       <s:c r="C56" s="1" t="n">
         <s:v>14</s:v>
       </s:c>
-      <s:c r="D56" s="1"/>
-      <s:c r="E56" s="1"/>
+      <s:c r="D56" s="1" t="n">
+        <s:v>1200</s:v>
+      </s:c>
+      <s:c r="E56" s="1" t="n">
+        <s:v>349.72</s:v>
+      </s:c>
       <s:c r="F56" s="1" t="n">
         <s:v>-2385</s:v>
       </s:c>
@@ -6622,8 +6842,12 @@
       <s:c r="C57" s="1" t="n">
         <s:v>14</s:v>
       </s:c>
-      <s:c r="D57" s="1"/>
-      <s:c r="E57" s="1"/>
+      <s:c r="D57" s="1" t="n">
+        <s:v>1200</s:v>
+      </s:c>
+      <s:c r="E57" s="1" t="n">
+        <s:v>348.57</s:v>
+      </s:c>
       <s:c r="F57" s="1" t="n">
         <s:v>-1615</s:v>
       </s:c>
@@ -6668,8 +6892,12 @@
       <s:c r="C58" s="1" t="n">
         <s:v>15</s:v>
       </s:c>
-      <s:c r="D58" s="1"/>
-      <s:c r="E58" s="1"/>
+      <s:c r="D58" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="E58" s="1" t="n">
+        <s:v>346.89</s:v>
+      </s:c>
       <s:c r="F58" s="1" t="n">
         <s:v>-760</s:v>
       </s:c>
@@ -6714,8 +6942,12 @@
       <s:c r="C59" s="1" t="n">
         <s:v>15</s:v>
       </s:c>
-      <s:c r="D59" s="1"/>
-      <s:c r="E59" s="1"/>
+      <s:c r="D59" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="E59" s="1" t="n">
+        <s:v>357.89</s:v>
+      </s:c>
       <s:c r="F59" s="1" t="n">
         <s:v>-650</s:v>
       </s:c>
@@ -6760,8 +6992,12 @@
       <s:c r="C60" s="1" t="n">
         <s:v>15</s:v>
       </s:c>
-      <s:c r="D60" s="1"/>
-      <s:c r="E60" s="1"/>
+      <s:c r="D60" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="E60" s="1" t="n">
+        <s:v>349.95</s:v>
+      </s:c>
       <s:c r="F60" s="1" t="n">
         <s:v>-370</s:v>
       </s:c>
@@ -6806,8 +7042,12 @@
       <s:c r="C61" s="1" t="n">
         <s:v>15</s:v>
       </s:c>
-      <s:c r="D61" s="1"/>
-      <s:c r="E61" s="1"/>
+      <s:c r="D61" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="E61" s="1" t="n">
+        <s:v>358.92</s:v>
+      </s:c>
       <s:c r="F61" s="1" t="n">
         <s:v>-190</s:v>
       </s:c>
@@ -6852,8 +7092,12 @@
       <s:c r="C62" s="1" t="n">
         <s:v>16</s:v>
       </s:c>
-      <s:c r="D62" s="1"/>
-      <s:c r="E62" s="1"/>
+      <s:c r="D62" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="E62" s="1" t="n">
+        <s:v>358.19</s:v>
+      </s:c>
       <s:c r="F62" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -6898,8 +7142,12 @@
       <s:c r="C63" s="1" t="n">
         <s:v>16</s:v>
       </s:c>
-      <s:c r="D63" s="1"/>
-      <s:c r="E63" s="1"/>
+      <s:c r="D63" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="E63" s="1" t="n">
+        <s:v>350</s:v>
+      </s:c>
       <s:c r="F63" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -6944,8 +7192,12 @@
       <s:c r="C64" s="1" t="n">
         <s:v>16</s:v>
       </s:c>
-      <s:c r="D64" s="1"/>
-      <s:c r="E64" s="1"/>
+      <s:c r="D64" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="E64" s="1" t="n">
+        <s:v>377.44</s:v>
+      </s:c>
       <s:c r="F64" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -6990,8 +7242,12 @@
       <s:c r="C65" s="1" t="n">
         <s:v>16</s:v>
       </s:c>
-      <s:c r="D65" s="1"/>
-      <s:c r="E65" s="1"/>
+      <s:c r="D65" s="1" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="E65" s="1" t="n">
+        <s:v>377.44</s:v>
+      </s:c>
       <s:c r="F65" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -7036,8 +7292,12 @@
       <s:c r="C66" s="1" t="n">
         <s:v>17</s:v>
       </s:c>
-      <s:c r="D66" s="1"/>
-      <s:c r="E66" s="1"/>
+      <s:c r="D66" s="1" t="n">
+        <s:v>423.51</s:v>
+      </s:c>
+      <s:c r="E66" s="1" t="n">
+        <s:v>375.42</s:v>
+      </s:c>
       <s:c r="F66" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -7082,8 +7342,12 @@
       <s:c r="C67" s="1" t="n">
         <s:v>17</s:v>
       </s:c>
-      <s:c r="D67" s="1"/>
-      <s:c r="E67" s="1"/>
+      <s:c r="D67" s="1" t="n">
+        <s:v>423.51</s:v>
+      </s:c>
+      <s:c r="E67" s="1" t="n">
+        <s:v>384.11</s:v>
+      </s:c>
       <s:c r="F67" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -7128,8 +7392,12 @@
       <s:c r="C68" s="1" t="n">
         <s:v>17</s:v>
       </s:c>
-      <s:c r="D68" s="1"/>
-      <s:c r="E68" s="1"/>
+      <s:c r="D68" s="1" t="n">
+        <s:v>423.51</s:v>
+      </s:c>
+      <s:c r="E68" s="1" t="n">
+        <s:v>386.01</s:v>
+      </s:c>
       <s:c r="F68" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -7174,8 +7442,12 @@
       <s:c r="C69" s="1" t="n">
         <s:v>17</s:v>
       </s:c>
-      <s:c r="D69" s="1"/>
-      <s:c r="E69" s="1"/>
+      <s:c r="D69" s="1" t="n">
+        <s:v>423.51</s:v>
+      </s:c>
+      <s:c r="E69" s="1" t="n">
+        <s:v>375.51</s:v>
+      </s:c>
       <s:c r="F69" s="1" t="n">
         <s:v>100</s:v>
       </s:c>
@@ -7220,8 +7492,12 @@
       <s:c r="C70" s="1" t="n">
         <s:v>18</s:v>
       </s:c>
-      <s:c r="D70" s="1"/>
-      <s:c r="E70" s="1"/>
+      <s:c r="D70" s="1" t="n">
+        <s:v>433.19</s:v>
+      </s:c>
+      <s:c r="E70" s="1" t="n">
+        <s:v>394.45</s:v>
+      </s:c>
       <s:c r="F70" s="1" t="n">
         <s:v>330</s:v>
       </s:c>
@@ -7266,8 +7542,12 @@
       <s:c r="C71" s="1" t="n">
         <s:v>18</s:v>
       </s:c>
-      <s:c r="D71" s="1"/>
-      <s:c r="E71" s="1"/>
+      <s:c r="D71" s="1" t="n">
+        <s:v>433.19</s:v>
+      </s:c>
+      <s:c r="E71" s="1" t="n">
+        <s:v>403.39</s:v>
+      </s:c>
       <s:c r="F71" s="1" t="n">
         <s:v>850</s:v>
       </s:c>
@@ -7312,8 +7592,12 @@
       <s:c r="C72" s="1" t="n">
         <s:v>18</s:v>
       </s:c>
-      <s:c r="D72" s="1"/>
-      <s:c r="E72" s="1"/>
+      <s:c r="D72" s="1" t="n">
+        <s:v>433.19</s:v>
+      </s:c>
+      <s:c r="E72" s="1" t="n">
+        <s:v>403.42</s:v>
+      </s:c>
       <s:c r="F72" s="1" t="n">
         <s:v>1125</s:v>
       </s:c>
@@ -7358,8 +7642,12 @@
       <s:c r="C73" s="1" t="n">
         <s:v>18</s:v>
       </s:c>
-      <s:c r="D73" s="1"/>
-      <s:c r="E73" s="1"/>
+      <s:c r="D73" s="1" t="n">
+        <s:v>433.19</s:v>
+      </s:c>
+      <s:c r="E73" s="1" t="n">
+        <s:v>415.07</s:v>
+      </s:c>
       <s:c r="F73" s="1" t="n">
         <s:v>1185</s:v>
       </s:c>
@@ -7404,8 +7692,12 @@
       <s:c r="C74" s="1" t="n">
         <s:v>19</s:v>
       </s:c>
-      <s:c r="D74" s="1"/>
-      <s:c r="E74" s="1"/>
+      <s:c r="D74" s="1" t="n">
+        <s:v>433.19</s:v>
+      </s:c>
+      <s:c r="E74" s="1" t="n">
+        <s:v>417.66</s:v>
+      </s:c>
       <s:c r="F74" s="1" t="n">
         <s:v>1595</s:v>
       </s:c>
@@ -7450,8 +7742,12 @@
       <s:c r="C75" s="1" t="n">
         <s:v>19</s:v>
       </s:c>
-      <s:c r="D75" s="1"/>
-      <s:c r="E75" s="1"/>
+      <s:c r="D75" s="1" t="n">
+        <s:v>433.19</s:v>
+      </s:c>
+      <s:c r="E75" s="1" t="n">
+        <s:v>424.2</s:v>
+      </s:c>
       <s:c r="F75" s="1" t="n">
         <s:v>1625</s:v>
       </s:c>
@@ -7496,8 +7792,12 @@
       <s:c r="C76" s="1" t="n">
         <s:v>19</s:v>
       </s:c>
-      <s:c r="D76" s="1"/>
-      <s:c r="E76" s="1"/>
+      <s:c r="D76" s="1" t="n">
+        <s:v>433.19</s:v>
+      </s:c>
+      <s:c r="E76" s="1" t="n">
+        <s:v>424.76</s:v>
+      </s:c>
       <s:c r="F76" s="1" t="n">
         <s:v>1685</s:v>
       </s:c>
@@ -7542,8 +7842,12 @@
       <s:c r="C77" s="1" t="n">
         <s:v>19</s:v>
       </s:c>
-      <s:c r="D77" s="1"/>
-      <s:c r="E77" s="1"/>
+      <s:c r="D77" s="1" t="n">
+        <s:v>433.19</s:v>
+      </s:c>
+      <s:c r="E77" s="1" t="n">
+        <s:v>424.85</s:v>
+      </s:c>
       <s:c r="F77" s="1" t="n">
         <s:v>1765</s:v>
       </s:c>
@@ -7588,8 +7892,12 @@
       <s:c r="C78" s="1" t="n">
         <s:v>20</s:v>
       </s:c>
-      <s:c r="D78" s="1"/>
-      <s:c r="E78" s="1"/>
+      <s:c r="D78" s="1" t="n">
+        <s:v>433.19</s:v>
+      </s:c>
+      <s:c r="E78" s="1" t="n">
+        <s:v>424.98</s:v>
+      </s:c>
       <s:c r="F78" s="1" t="n">
         <s:v>1440</s:v>
       </s:c>
@@ -7634,8 +7942,12 @@
       <s:c r="C79" s="1" t="n">
         <s:v>20</s:v>
       </s:c>
-      <s:c r="D79" s="1"/>
-      <s:c r="E79" s="1"/>
+      <s:c r="D79" s="1" t="n">
+        <s:v>433.19</s:v>
+      </s:c>
+      <s:c r="E79" s="1" t="n">
+        <s:v>424.76</s:v>
+      </s:c>
       <s:c r="F79" s="1" t="n">
         <s:v>1190</s:v>
       </s:c>
@@ -7680,8 +7992,12 @@
       <s:c r="C80" s="1" t="n">
         <s:v>20</s:v>
       </s:c>
-      <s:c r="D80" s="1"/>
-      <s:c r="E80" s="1"/>
+      <s:c r="D80" s="1" t="n">
+        <s:v>433.19</s:v>
+      </s:c>
+      <s:c r="E80" s="1" t="n">
+        <s:v>424.98</s:v>
+      </s:c>
       <s:c r="F80" s="1" t="n">
         <s:v>710</s:v>
       </s:c>
@@ -7726,8 +8042,12 @@
       <s:c r="C81" s="1" t="n">
         <s:v>20</s:v>
       </s:c>
-      <s:c r="D81" s="1"/>
-      <s:c r="E81" s="1"/>
+      <s:c r="D81" s="1" t="n">
+        <s:v>433.19</s:v>
+      </s:c>
+      <s:c r="E81" s="1" t="n">
+        <s:v>417.95</s:v>
+      </s:c>
       <s:c r="F81" s="1" t="n">
         <s:v>520</s:v>
       </s:c>
@@ -7772,8 +8092,12 @@
       <s:c r="C82" s="1" t="n">
         <s:v>21</s:v>
       </s:c>
-      <s:c r="D82" s="1"/>
-      <s:c r="E82" s="1"/>
+      <s:c r="D82" s="1" t="n">
+        <s:v>433.19</s:v>
+      </s:c>
+      <s:c r="E82" s="1" t="n">
+        <s:v>414.58</s:v>
+      </s:c>
       <s:c r="F82" s="1" t="n">
         <s:v>400</s:v>
       </s:c>
@@ -7818,8 +8142,12 @@
       <s:c r="C83" s="1" t="n">
         <s:v>21</s:v>
       </s:c>
-      <s:c r="D83" s="1"/>
-      <s:c r="E83" s="1"/>
+      <s:c r="D83" s="1" t="n">
+        <s:v>433.19</s:v>
+      </s:c>
+      <s:c r="E83" s="1" t="n">
+        <s:v>414.36</s:v>
+      </s:c>
       <s:c r="F83" s="1" t="n">
         <s:v>320</s:v>
       </s:c>
@@ -7864,8 +8192,12 @@
       <s:c r="C84" s="1" t="n">
         <s:v>21</s:v>
       </s:c>
-      <s:c r="D84" s="1"/>
-      <s:c r="E84" s="1"/>
+      <s:c r="D84" s="1" t="n">
+        <s:v>433.19</s:v>
+      </s:c>
+      <s:c r="E84" s="1" t="n">
+        <s:v>415.83</s:v>
+      </s:c>
       <s:c r="F84" s="1" t="n">
         <s:v>180</s:v>
       </s:c>
@@ -7910,8 +8242,12 @@
       <s:c r="C85" s="1" t="n">
         <s:v>21</s:v>
       </s:c>
-      <s:c r="D85" s="1"/>
-      <s:c r="E85" s="1"/>
+      <s:c r="D85" s="1" t="n">
+        <s:v>433.19</s:v>
+      </s:c>
+      <s:c r="E85" s="1" t="n">
+        <s:v>404.58</s:v>
+      </s:c>
       <s:c r="F85" s="1" t="n">
         <s:v>100</s:v>
       </s:c>
@@ -7956,8 +8292,12 @@
       <s:c r="C86" s="1" t="n">
         <s:v>22</s:v>
       </s:c>
-      <s:c r="D86" s="1"/>
-      <s:c r="E86" s="1"/>
+      <s:c r="D86" s="1" t="n">
+        <s:v>433.19</s:v>
+      </s:c>
+      <s:c r="E86" s="1" t="n">
+        <s:v>394.45</s:v>
+      </s:c>
       <s:c r="F86" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -8002,8 +8342,12 @@
       <s:c r="C87" s="1" t="n">
         <s:v>22</s:v>
       </s:c>
-      <s:c r="D87" s="1"/>
-      <s:c r="E87" s="1"/>
+      <s:c r="D87" s="1" t="n">
+        <s:v>433.19</s:v>
+      </s:c>
+      <s:c r="E87" s="1" t="n">
+        <s:v>396.05</s:v>
+      </s:c>
       <s:c r="F87" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -8048,8 +8392,12 @@
       <s:c r="C88" s="1" t="n">
         <s:v>22</s:v>
       </s:c>
-      <s:c r="D88" s="1"/>
-      <s:c r="E88" s="1"/>
+      <s:c r="D88" s="1" t="n">
+        <s:v>433.19</s:v>
+      </s:c>
+      <s:c r="E88" s="1" t="n">
+        <s:v>403.42</s:v>
+      </s:c>
       <s:c r="F88" s="1" t="n">
         <s:v>100</s:v>
       </s:c>
@@ -8094,8 +8442,12 @@
       <s:c r="C89" s="1" t="n">
         <s:v>22</s:v>
       </s:c>
-      <s:c r="D89" s="1"/>
-      <s:c r="E89" s="1"/>
+      <s:c r="D89" s="1" t="n">
+        <s:v>433.19</s:v>
+      </s:c>
+      <s:c r="E89" s="1" t="n">
+        <s:v>402.45</s:v>
+      </s:c>
       <s:c r="F89" s="1" t="n">
         <s:v>200</s:v>
       </s:c>
@@ -8140,8 +8492,12 @@
       <s:c r="C90" s="1" t="n">
         <s:v>23</s:v>
       </s:c>
-      <s:c r="D90" s="1"/>
-      <s:c r="E90" s="1"/>
+      <s:c r="D90" s="1" t="n">
+        <s:v>433.19</s:v>
+      </s:c>
+      <s:c r="E90" s="1" t="n">
+        <s:v>395.41</s:v>
+      </s:c>
       <s:c r="F90" s="1" t="n">
         <s:v>750</s:v>
       </s:c>
@@ -8186,8 +8542,12 @@
       <s:c r="C91" s="1" t="n">
         <s:v>23</s:v>
       </s:c>
-      <s:c r="D91" s="1"/>
-      <s:c r="E91" s="1"/>
+      <s:c r="D91" s="1" t="n">
+        <s:v>433.19</s:v>
+      </s:c>
+      <s:c r="E91" s="1" t="n">
+        <s:v>403.39</s:v>
+      </s:c>
       <s:c r="F91" s="1" t="n">
         <s:v>900</s:v>
       </s:c>
@@ -8232,8 +8592,12 @@
       <s:c r="C92" s="1" t="n">
         <s:v>23</s:v>
       </s:c>
-      <s:c r="D92" s="1"/>
-      <s:c r="E92" s="1"/>
+      <s:c r="D92" s="1" t="n">
+        <s:v>433.19</s:v>
+      </s:c>
+      <s:c r="E92" s="1" t="n">
+        <s:v>393.91</s:v>
+      </s:c>
       <s:c r="F92" s="1" t="n">
         <s:v>930</s:v>
       </s:c>
@@ -8278,8 +8642,12 @@
       <s:c r="C93" s="1" t="n">
         <s:v>23</s:v>
       </s:c>
-      <s:c r="D93" s="1"/>
-      <s:c r="E93" s="1"/>
+      <s:c r="D93" s="1" t="n">
+        <s:v>433.19</s:v>
+      </s:c>
+      <s:c r="E93" s="1" t="n">
+        <s:v>404.66</s:v>
+      </s:c>
       <s:c r="F93" s="1" t="n">
         <s:v>640</s:v>
       </s:c>
@@ -8324,8 +8692,12 @@
       <s:c r="C94" s="1" t="n">
         <s:v>24</s:v>
       </s:c>
-      <s:c r="D94" s="1"/>
-      <s:c r="E94" s="1"/>
+      <s:c r="D94" s="1" t="n">
+        <s:v>433.19</s:v>
+      </s:c>
+      <s:c r="E94" s="1" t="n">
+        <s:v>414.82</s:v>
+      </s:c>
       <s:c r="F94" s="1" t="n">
         <s:v>590</s:v>
       </s:c>
@@ -8370,8 +8742,12 @@
       <s:c r="C95" s="1" t="n">
         <s:v>24</s:v>
       </s:c>
-      <s:c r="D95" s="1"/>
-      <s:c r="E95" s="1"/>
+      <s:c r="D95" s="1" t="n">
+        <s:v>433.19</s:v>
+      </s:c>
+      <s:c r="E95" s="1" t="n">
+        <s:v>414.58</s:v>
+      </s:c>
       <s:c r="F95" s="1" t="n">
         <s:v>590</s:v>
       </s:c>
@@ -8416,8 +8792,12 @@
       <s:c r="C96" s="1" t="n">
         <s:v>24</s:v>
       </s:c>
-      <s:c r="D96" s="1"/>
-      <s:c r="E96" s="1"/>
+      <s:c r="D96" s="1" t="n">
+        <s:v>433.19</s:v>
+      </s:c>
+      <s:c r="E96" s="1" t="n">
+        <s:v>404.98</s:v>
+      </s:c>
       <s:c r="F96" s="1" t="n">
         <s:v>360</s:v>
       </s:c>
@@ -8464,8 +8844,12 @@
       <s:c r="C97" s="1" t="n">
         <s:v>24</s:v>
       </s:c>
-      <s:c r="D97" s="1"/>
-      <s:c r="E97" s="1"/>
+      <s:c r="D97" s="1" t="n">
+        <s:v>433.19</s:v>
+      </s:c>
+      <s:c r="E97" s="1" t="n">
+        <s:v>405.29</s:v>
+      </s:c>
       <s:c r="F97" s="1" t="n">
         <s:v>290</s:v>
       </s:c>
